--- a/samples/C_科目余额表.xlsx
+++ b/samples/C_科目余额表.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -643,96 +643,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>1122</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>应收账款</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>1680000</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>38600000</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>38350000</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>1850000</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>1403</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>原材料</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>3200000</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>8500000</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>7900000</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>3800000</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2202</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>应付账款</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>2350000</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>18000000</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>18250000</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>2600000</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
